--- a/public/post/drafts/season-prediction/men_model-exhaustive-tests-r2.xlsx
+++ b/public/post/drafts/season-prediction/men_model-exhaustive-tests-r2.xlsx
@@ -561,25 +561,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>0.663658761789832</v>
+        <v>0.660670142707309</v>
       </c>
       <c r="C7" t="n">
-        <v>0.71045577197318</v>
+        <v>0.717139867169552</v>
       </c>
       <c r="D7" t="n">
-        <v>0.488079312088485</v>
+        <v>0.489761488073691</v>
       </c>
       <c r="E7" t="n">
-        <v>0.62691681075055</v>
+        <v>0.62787778005051</v>
       </c>
       <c r="F7" t="n">
-        <v>0.762791935505646</v>
+        <v>0.757845669630354</v>
       </c>
       <c r="G7" t="n">
-        <v>0.650478152661505</v>
+        <v>0.650661060464063</v>
       </c>
       <c r="H7" t="n">
-        <v>0.650396790794866</v>
+        <v>0.65065933468258</v>
       </c>
     </row>
     <row r="8">
